--- a/data/northstar/Northstar-Disposition-Analysis-v1.xlsx
+++ b/data/northstar/Northstar-Disposition-Analysis-v1.xlsx
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Produced 2026-08-14 by Aberdeen Advisors' Application Rationalization engine. Source: the 20-application sample dataset Bina Din's team built (F0BQCGAM8E5.xlsx, 11 sheets). Her file was opened read-only and is unchanged.</t>
+          <t>Produced 2026-08-14 by Aberdeen Advisors' Application Rationalization engine. Source: the 20-application sample dataset Bina Din's team built (healthcare_app_rationalization_sample_20.xlsx, 11 sheets). Her file was opened read-only and is unchanged.</t>
         </is>
       </c>
     </row>
